--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2180,6 +2180,115 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127275096</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90796</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>720</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Yttre Munkhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>507667</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6607499</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>127275096</v>
       </c>
       <c r="B14" t="n">
-        <v>90796</v>
+        <v>90802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>127275096</v>
       </c>
       <c r="B14" t="n">
-        <v>90802</v>
+        <v>90803</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>127275096</v>
       </c>
       <c r="B14" t="n">
-        <v>90803</v>
+        <v>90807</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>127275096</v>
       </c>
       <c r="B14" t="n">
-        <v>90807</v>
+        <v>90809</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>127275096</v>
       </c>
       <c r="B14" t="n">
-        <v>90809</v>
+        <v>90815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>127275096</v>
       </c>
       <c r="B14" t="n">
-        <v>90815</v>
+        <v>90818</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>127275096</v>
       </c>
       <c r="B14" t="n">
-        <v>90818</v>
+        <v>90826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>127275096</v>
       </c>
       <c r="B14" t="n">
-        <v>90826</v>
+        <v>90827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>127275096</v>
       </c>
       <c r="B14" t="n">
-        <v>90827</v>
+        <v>90796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 21177-2021 artfynd.xlsx
+++ b/artfynd/A 21177-2021 artfynd.xlsx
@@ -2185,7 +2185,7 @@
         <v>127275096</v>
       </c>
       <c r="B14" t="n">
-        <v>90796</v>
+        <v>90827</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
